--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -618,7 +618,7 @@
     <t>この画像検査が関連しているEncounterリソース</t>
   </si>
   <si>
-    <t>このImagingStudyが行われるヘルスケアイベント（患者とヘルスケアプロバイダの相互作用など）。</t>
+    <t>このImagingStudyが行われる診療イベント（患者と医療提供者の相互作用など）。</t>
   </si>
   <si>
     <t>これは通常、イベントが発生したEncounterであるが、一部のイベントは、Encounterの正式な完了の前または後に開始される場合があり、それでもそのEncounterのコンテキストに関連付けられている（例：入院前の検査）  
@@ -1014,8 +1014,7 @@
     <t>スタディのイメージングマネージャの説明。実施されたスタディ（コンポーネント）の機関生成の説明または分類。</t>
   </si>
   <si>
-    <t>FHIR文字列のサイズは1MBを超えてはならないことに注意。  
-検査に関するフリーコメント。</t>
+    <t>検査に関するフリーコメント。</t>
   </si>
   <si>
     <t>.text</t>
@@ -1167,8 +1166,7 @@
     <t>シリーズの記述。</t>
   </si>
   <si>
-    <t>FHIR文字列のサイズは1MBを超えてはならないことに注意。  
-シリーズごとにつけられるフリーコメント。</t>
+    <t>シリーズごとにつけられるフリーコメント。</t>
   </si>
   <si>
     <t>CT Surview 180</t>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -865,7 +865,7 @@
     <t>実施されたProcedureのタイプを表すコード。</t>
   </si>
   <si>
-    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係と調整前後の関係を管理するための独自の構造を提供する必要がある。  
+    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用して、テキスト、`Coding`、翻訳、および要素間の関係と調整前後の関係を管理するための独自の構造を提供する必要がある。  
 エラーコードなどを記載</t>
   </si>
   <si>
@@ -922,7 +922,7 @@
     <t>ImagingStudyが要求された理由を示す臨床状態の説明。</t>
   </si>
   <si>
-    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係と調整前後の関係を管理するための独自の構造を提供する必要がある。  
+    <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、`Coding`を直接使用して、テキスト、`Coding`、翻訳、および要素間の関係と調整前後の関係を管理するための独自の構造を提供する必要がある。  
 JP Coreでは未使用</t>
   </si>
   <si>
@@ -980,14 +980,14 @@
 </t>
   </si>
   <si>
-    <t>ユーザが定義したコメント</t>
+    <t>ユーザーが定義したコメント</t>
   </si>
   <si>
     <t>推奨されるDICOMマッピングによると、この要素はスタディの説明属性（0008,1030）から派生している。画像検査に関する観察または所見は、この要素に記述するのではなく、Observationのような別のリソースに記録する必要がある。</t>
   </si>
   <si>
     <t>構造化された注釈（アノテーション）を持たないシステムの場合、作成者や時間なしで単一の注釈を簡単に伝達できる。情報を変更する可能性があるため、この要素をナラティブに含める必要がある場合がある。  
-*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。  
+*注釈は、計算機処理れきる「変更」情報を伝達するために使用されるべきではない*。 （ユーザーの行動を強制することはほとんど不可能であるため、これはSHOULDとする）。  
 コメント（Annotation型による記述）</t>
   </si>
   <si>
@@ -1120,7 +1120,7 @@
   </si>
   <si>
     <t>32ビット数で表す。これより大きい値の場合は、10進数を使用する。  
-上記UIDとは別に、ユーザ（または装置）が自由に決められる番号。</t>
+上記UIDとは別に、ユーザー（または装置）が自由に決められる番号。</t>
   </si>
   <si>
     <t>3</t>
@@ -1273,7 +1273,7 @@
   </si>
   <si>
     <t>参照は、実在のFHIRリソースへの参照である必要があり、内容に辿り着ける（解決できる）必要がある（アクセス制御、一時的な使用不可などを考慮に入れる）。解決は、URLから取得するか、リソースタイプによって該当する場合は、絶対参照を正規URLとして扱い、ローカルレジストリ/リポジトリで検索することによって行うことができる。  
-【JP Core仕様】UIDは別のtagが存在するので、ユーザ側で自由に付与していい番号と思われる。</t>
+【JP Core仕様】UIDは別のtagが存在するので、ユーザー側で自由に付与していい番号と思われる。</t>
   </si>
   <si>
     <t>Role[classCode=SPEC]</t>
@@ -1471,7 +1471,7 @@
   </si>
   <si>
     <t>32ビット数で表す。これより大きい値の場合は、10進数を使用する。  
-【JP Core仕様】ユーザ（または装置）が自由に決められる画像ごとの番号。DICOMタグマッピングにある値をそのまま設定。</t>
+【JP Core仕様】ユーザー（または装置）が自由に決められる画像ごとの番号。DICOMタグマッピングにある値をそのまま設定。</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP, source[classCode=OBSSER, moodCode=EVN]].sequenceNumber</t>
